--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9798,0.0007,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.9451,0.0006,0.0005,0.0524</t>
-  </si>
-  <si>
-    <t>0.9532,0.0009,0.0034,0.0157</t>
-  </si>
-  <si>
-    <t>0.9419,0.0011,0.0038,0.0376</t>
-  </si>
-  <si>
-    <t>0.9482,0.0017,0.0014,0.0456</t>
-  </si>
-  <si>
-    <t>0.6390,0.0044,0.0006,0.2322</t>
-  </si>
-  <si>
-    <t>0.8827,0.0048,0.0035,0.0953</t>
-  </si>
-  <si>
-    <t>0.9558,0.0014,0.0015,0.0348</t>
-  </si>
-  <si>
-    <t>0.5715,0.0108,0.0157,0.4647</t>
-  </si>
-  <si>
-    <t>0.8583,0.0158,0.0083,0.0631</t>
-  </si>
-  <si>
-    <t>0.8797,0.0025,0.0012,0.1124</t>
-  </si>
-  <si>
-    <t>0.9447,0.0008,0.0007,0.0746</t>
-  </si>
-  <si>
-    <t>0.9581,0.0045,0.0276,0.0010</t>
-  </si>
-  <si>
-    <t>0.8608,0.0053,0.1204,0.0107</t>
-  </si>
-  <si>
-    <t>0.8868,0.0065,0.1467,0.0010</t>
-  </si>
-  <si>
-    <t>0.8226,0.0087,0.2508,0.0024</t>
-  </si>
-  <si>
-    <t>0.9702,0.0008,0.0233,0.0009</t>
-  </si>
-  <si>
-    <t>0.7088,0.2435,0.0308,0.0010</t>
-  </si>
-  <si>
-    <t>0.8674,0.0678,0.0214,0.0008</t>
-  </si>
-  <si>
-    <t>0.9905,0.0012,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.6800,0.1838,0.0968,0.0029</t>
-  </si>
-  <si>
-    <t>0.7323,0.2662,0.0095,0.0007</t>
-  </si>
-  <si>
-    <t>0.9556,0.0016,0.0360,0.0013</t>
-  </si>
-  <si>
-    <t>0.9213,0.0050,0.0628,0.0016</t>
-  </si>
-  <si>
-    <t>0.7859,0.0021,0.2573,0.0025</t>
-  </si>
-  <si>
-    <t>0.8960,0.0011,0.1911,0.0005</t>
-  </si>
-  <si>
-    <t>0.9430,0.0018,0.0912,0.0004</t>
-  </si>
-  <si>
-    <t>0.9207,0.0037,0.0945,0.0020</t>
-  </si>
-  <si>
-    <t>0.1310,0.0231,0.9401,0.0014</t>
-  </si>
-  <si>
-    <t>0.9232,0.0168,0.0399,0.0031</t>
-  </si>
-  <si>
-    <t>0.8225,0.1244,0.0311,0.0040</t>
-  </si>
-  <si>
-    <t>0.0561,0.0513,0.9604,0.0051</t>
-  </si>
-  <si>
-    <t>0.9286,0.0512,0.0105,0.0007</t>
-  </si>
-  <si>
-    <t>0.9747,0.0044,0.0027,0.0020</t>
-  </si>
-  <si>
-    <t>0.9252,0.0060,0.0714,0.0063</t>
-  </si>
-  <si>
-    <t>0.9436,0.0043,0.0145,0.0097</t>
-  </si>
-  <si>
-    <t>0.9512,0.0091,0.0243,0.0024</t>
-  </si>
-  <si>
-    <t>0.0501,0.3626,0.8866,0.0077</t>
-  </si>
-  <si>
-    <t>0.7016,0.0069,0.4629,0.0011</t>
-  </si>
-  <si>
-    <t>0.8081,0.0042,0.3640,0.0006</t>
-  </si>
-  <si>
-    <t>0.2186,0.0157,0.8914,0.0032</t>
-  </si>
-  <si>
-    <t>0.8847,0.0065,0.1830,0.0005</t>
-  </si>
-  <si>
-    <t>0.0093,0.9857,0.0264,0.0001</t>
-  </si>
-  <si>
-    <t>0.5947,0.0081,0.5961,0.0015</t>
-  </si>
-  <si>
-    <t>0.7725,0.0580,0.1466,0.0103</t>
-  </si>
-  <si>
-    <t>0.9799,0.0051,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.9885,0.0029,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9744,0.0104,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.0960,0.0576,0.9088,0.0017</t>
-  </si>
-  <si>
-    <t>0.5540,0.0212,0.6114,0.0007</t>
-  </si>
-  <si>
-    <t>0.9489,0.0007,0.0784,0.0007</t>
-  </si>
-  <si>
-    <t>0.5732,0.0242,0.6006,0.0029</t>
-  </si>
-  <si>
-    <t>0.3376,0.0555,0.7065,0.0015</t>
-  </si>
-  <si>
-    <t>0.1782,0.0087,0.8728,0.0021</t>
-  </si>
-  <si>
-    <t>0.8763,0.0053,0.0036,0.0843</t>
-  </si>
-  <si>
-    <t>0.7181,0.0900,0.0342,0.0341</t>
-  </si>
-  <si>
-    <t>0.7605,0.0103,0.0231,0.2105</t>
-  </si>
-  <si>
-    <t>0.0958,0.2791,0.8182,0.0230</t>
-  </si>
-  <si>
-    <t>0.9062,0.0079,0.0150,0.0508</t>
-  </si>
-  <si>
-    <t>0.9500,0.0033,0.0025,0.0201</t>
-  </si>
-  <si>
-    <t>0.9232,0.0084,0.0109,0.0309</t>
-  </si>
-  <si>
-    <t>0.0406,0.6193,0.9042,0.0007</t>
-  </si>
-  <si>
-    <t>0.4628,0.0100,0.6900,0.0008</t>
-  </si>
-  <si>
-    <t>0.3608,0.0019,0.8801,0.0001</t>
-  </si>
-  <si>
-    <t>0.0118,0.5759,0.9665,0.0006</t>
-  </si>
-  <si>
-    <t>0.1270,0.0010,0.9503,0.0001</t>
-  </si>
-  <si>
-    <t>0.5659,0.4246,0.0186,0.0009</t>
-  </si>
-  <si>
-    <t>0.3622,0.7420,0.0094,0.0007</t>
-  </si>
-  <si>
-    <t>0.9088,0.0067,0.0805,0.0021</t>
-  </si>
-  <si>
-    <t>0.9142,0.0039,0.0684,0.0026</t>
-  </si>
-  <si>
-    <t>0.0244,0.2889,0.9499,0.0036</t>
-  </si>
-  <si>
-    <t>0.8286,0.0135,0.2495,0.0010</t>
-  </si>
-  <si>
-    <t>0.7652,0.0075,0.3810,0.0003</t>
-  </si>
-  <si>
-    <t>0.0268,0.9694,0.2441,0.0007</t>
-  </si>
-  <si>
-    <t>0.0764,0.7570,0.3637,0.0005</t>
-  </si>
-  <si>
-    <t>0.8534,0.0029,0.0216,0.0520</t>
-  </si>
-  <si>
-    <t>0.9080,0.0002,0.0009,0.1187</t>
-  </si>
-  <si>
-    <t>0.4850,0.0003,0.0031,0.6967</t>
-  </si>
-  <si>
-    <t>0.6485,0.0001,0.0035,0.2785</t>
-  </si>
-  <si>
-    <t>0.9374,0.0009,0.0041,0.0466</t>
-  </si>
-  <si>
-    <t>0.9370,0.0004,0.0015,0.0663</t>
-  </si>
-  <si>
-    <t>0.3142,0.2465,0.5706,0.0017</t>
-  </si>
-  <si>
-    <t>0.2173,0.0154,0.8899,0.0001</t>
-  </si>
-  <si>
-    <t>0.7169,0.0126,0.4406,0.0003</t>
-  </si>
-  <si>
-    <t>0.0636,0.0179,0.9641,0.0004</t>
-  </si>
-  <si>
-    <t>0.2092,0.3056,0.5380,0.0004</t>
-  </si>
-  <si>
-    <t>0.1984,0.0136,0.9325,0.0003</t>
-  </si>
-  <si>
-    <t>0.9393,0.0012,0.0033,0.0390</t>
-  </si>
-  <si>
-    <t>0.9364,0.0057,0.0059,0.0130</t>
-  </si>
-  <si>
-    <t>0.9602,0.0045,0.0018,0.0094</t>
-  </si>
-  <si>
-    <t>0.9252,0.0061,0.0041,0.0313</t>
-  </si>
-  <si>
-    <t>0.9460,0.0024,0.0010,0.0248</t>
-  </si>
-  <si>
-    <t>0.9277,0.0045,0.0030,0.0364</t>
-  </si>
-  <si>
-    <t>0.9016,0.0094,0.0084,0.0483</t>
-  </si>
-  <si>
-    <t>0.9797,0.0011,0.0014,0.0092</t>
-  </si>
-  <si>
-    <t>0.9491,0.0008,0.0009,0.0577</t>
-  </si>
-  <si>
-    <t>0.9509,0.0186,0.0066,0.0043</t>
-  </si>
-  <si>
-    <t>0.9291,0.0030,0.0039,0.0561</t>
-  </si>
-  <si>
-    <t>0.9273,0.0049,0.0073,0.0515</t>
-  </si>
-  <si>
-    <t>0.9228,0.0041,0.0010,0.0401</t>
-  </si>
-  <si>
-    <t>0.9438,0.0024,0.0026,0.0426</t>
-  </si>
-  <si>
-    <t>0.8524,0.0016,0.0013,0.2181</t>
-  </si>
-  <si>
-    <t>0.8562,0.0097,0.0055,0.0914</t>
-  </si>
-  <si>
-    <t>0.0950,0.0031,0.9688,0.0004</t>
-  </si>
-  <si>
-    <t>0.8211,0.0028,0.3631,0.0004</t>
-  </si>
-  <si>
-    <t>0.9926,0.0005,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.4189,0.0067,0.7880,0.0016</t>
-  </si>
-  <si>
-    <t>0.7566,0.1073,0.0347,0.0138</t>
-  </si>
-  <si>
-    <t>0.8198,0.0629,0.0288,0.0122</t>
-  </si>
-  <si>
-    <t>0.9035,0.0560,0.0230,0.0016</t>
-  </si>
-  <si>
-    <t>0.9643,0.0065,0.0056,0.0022</t>
-  </si>
-  <si>
-    <t>0.9287,0.0235,0.0066,0.0045</t>
-  </si>
-  <si>
-    <t>0.3007,0.7228,0.0563,0.0040</t>
-  </si>
-  <si>
-    <t>0.8741,0.0198,0.0383,0.0144</t>
-  </si>
-  <si>
-    <t>0.9431,0.0049,0.0554,0.0016</t>
-  </si>
-  <si>
-    <t>0.6913,0.0044,0.4509,0.0023</t>
-  </si>
-  <si>
-    <t>0.9744,0.0019,0.0132,0.0007</t>
-  </si>
-  <si>
-    <t>0.8944,0.0020,0.1058,0.0044</t>
-  </si>
-  <si>
-    <t>0.7751,0.0421,0.0669,0.0829</t>
-  </si>
-  <si>
-    <t>0.7938,0.1463,0.0312,0.0012</t>
-  </si>
-  <si>
-    <t>0.9624,0.0113,0.0080,0.0009</t>
-  </si>
-  <si>
-    <t>0.8698,0.0359,0.0770,0.0041</t>
-  </si>
-  <si>
-    <t>0.6736,0.3520,0.0208,0.0003</t>
-  </si>
-  <si>
-    <t>0.9700,0.0130,0.0044,0.0008</t>
-  </si>
-  <si>
-    <t>0.7394,0.0798,0.1269,0.0244</t>
-  </si>
-  <si>
-    <t>0.8871,0.0186,0.0278,0.0215</t>
-  </si>
-  <si>
-    <t>0.9696,0.0032,0.0089,0.0050</t>
-  </si>
-  <si>
-    <t>0.9301,0.0038,0.0083,0.0357</t>
-  </si>
-  <si>
-    <t>0.9090,0.0075,0.0048,0.0643</t>
-  </si>
-  <si>
-    <t>0.9696,0.0009,0.0056,0.0058</t>
-  </si>
-  <si>
-    <t>0.9820,0.0011,0.0010,0.0075</t>
-  </si>
-  <si>
-    <t>0.9571,0.0039,0.0093,0.0118</t>
-  </si>
-  <si>
-    <t>0.9621,0.0035,0.0026,0.0144</t>
-  </si>
-  <si>
-    <t>0.8990,0.0015,0.0039,0.0783</t>
-  </si>
-  <si>
-    <t>0.1299,0.1568,0.9175,0.0016</t>
-  </si>
-  <si>
-    <t>0.6909,0.0800,0.1740,0.0006</t>
-  </si>
-  <si>
-    <t>0.8851,0.0054,0.1742,0.0003</t>
-  </si>
-  <si>
-    <t>0.9204,0.0027,0.1271,0.0002</t>
-  </si>
-  <si>
-    <t>0.9759,0.0003,0.0136,0.0008</t>
-  </si>
-  <si>
-    <t>0.9600,0.0028,0.0101,0.0048</t>
-  </si>
-  <si>
-    <t>0.9274,0.0019,0.0984,0.0011</t>
-  </si>
-  <si>
-    <t>0.8535,0.0075,0.1214,0.0099</t>
-  </si>
-  <si>
-    <t>0.8588,0.0005,0.0105,0.0515</t>
-  </si>
-  <si>
-    <t>0.2640,0.0014,0.0106,0.8269</t>
-  </si>
-  <si>
-    <t>0.6845,0.0014,0.0102,0.3223</t>
-  </si>
-  <si>
-    <t>0.9647,0.0003,0.0068,0.0073</t>
-  </si>
-  <si>
-    <t>0.0323,0.2448,0.9300,0.0005</t>
-  </si>
-  <si>
-    <t>0.9856,0.0010,0.0020,0.0021</t>
-  </si>
-  <si>
-    <t>0.9344,0.0187,0.0180,0.0081</t>
-  </si>
-  <si>
-    <t>0.9609,0.0006,0.0010,0.0334</t>
-  </si>
-  <si>
-    <t>0.9344,0.0146,0.0072,0.0058</t>
-  </si>
-  <si>
-    <t>0.9570,0.0012,0.0018,0.0222</t>
-  </si>
-  <si>
-    <t>0.9281,0.0023,0.0017,0.0537</t>
-  </si>
-  <si>
-    <t>0.9578,0.0006,0.0011,0.0462</t>
-  </si>
-  <si>
-    <t>0.2488,0.0403,0.8402,0.0169</t>
-  </si>
-  <si>
-    <t>0.9353,0.0019,0.0032,0.0411</t>
-  </si>
-  <si>
-    <t>0.7536,0.0115,0.0131,0.2142</t>
-  </si>
-  <si>
-    <t>0.9742,0.0115,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.9869,0.0008,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9492,0.0057,0.0246,0.0024</t>
-  </si>
-  <si>
-    <t>0.8613,0.0202,0.0887,0.0084</t>
-  </si>
-  <si>
-    <t>0.9617,0.0104,0.0122,0.0007</t>
-  </si>
-  <si>
-    <t>0.9893,0.0006,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.8657,0.0034,0.0040,0.1348</t>
-  </si>
-  <si>
-    <t>0.9509,0.0002,0.0002,0.1095</t>
-  </si>
-  <si>
-    <t>0.9140,0.0177,0.0130,0.0208</t>
-  </si>
-  <si>
-    <t>0.8688,0.0025,0.0059,0.1430</t>
-  </si>
-  <si>
-    <t>0.8828,0.0006,0.0011,0.1617</t>
-  </si>
-  <si>
-    <t>0.7851,0.0222,0.0382,0.0601</t>
-  </si>
-  <si>
-    <t>0.8800,0.0016,0.0014,0.0998</t>
-  </si>
-  <si>
-    <t>0.8918,0.0040,0.0025,0.0985</t>
-  </si>
-  <si>
-    <t>0.7644,0.0853,0.0400,0.0205</t>
-  </si>
-  <si>
-    <t>0.9631,0.0070,0.0078,0.0025</t>
-  </si>
-  <si>
-    <t>0.9422,0.0100,0.0179,0.0041</t>
-  </si>
-  <si>
-    <t>0.3849,0.2974,0.6348,0.0518</t>
-  </si>
-  <si>
-    <t>0.9095,0.0207,0.0179,0.0120</t>
-  </si>
-  <si>
-    <t>0.9588,0.0007,0.0008,0.0333</t>
-  </si>
-  <si>
-    <t>0.9682,0.0075,0.0052,0.0020</t>
-  </si>
-  <si>
-    <t>0.9015,0.0090,0.0139,0.0350</t>
-  </si>
-  <si>
-    <t>0.0238,0.0404,0.9864,0.0013</t>
-  </si>
-  <si>
-    <t>0.9075,0.0096,0.0036,0.0202</t>
-  </si>
-  <si>
-    <t>0.2008,0.0199,0.8925,0.0009</t>
-  </si>
-  <si>
-    <t>0.5838,0.0103,0.6180,0.0007</t>
-  </si>
-  <si>
-    <t>0.7665,0.0026,0.3426,0.0015</t>
-  </si>
-  <si>
-    <t>0.4838,0.0211,0.7215,0.0007</t>
-  </si>
-  <si>
-    <t>0.0992,0.0076,0.9538,0.0007</t>
-  </si>
-  <si>
-    <t>0.0750,0.0058,0.9657,0.0006</t>
-  </si>
-  <si>
-    <t>0.9449,0.0006,0.0806,0.0006</t>
-  </si>
-  <si>
-    <t>0.8944,0.0022,0.1530,0.0020</t>
-  </si>
-  <si>
-    <t>0.9153,0.0034,0.0916,0.0012</t>
-  </si>
-  <si>
-    <t>0.9873,0.0003,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.9125,0.0080,0.0855,0.0011</t>
-  </si>
-  <si>
-    <t>0.9870,0.0012,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.9790,0.0005,0.0226,0.0003</t>
-  </si>
-  <si>
-    <t>0.9796,0.0008,0.0060,0.0017</t>
-  </si>
-  <si>
-    <t>0.9793,0.0007,0.0083,0.0015</t>
-  </si>
-  <si>
-    <t>0.6634,0.2473,0.0169,0.0094</t>
-  </si>
-  <si>
-    <t>0.1269,0.8582,0.0143,0.0037</t>
-  </si>
-  <si>
-    <t>0.9570,0.0287,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9530,0.0039,0.0049,0.0151</t>
-  </si>
-  <si>
-    <t>0.8221,0.0412,0.0072,0.0355</t>
-  </si>
-  <si>
-    <t>0.9172,0.0281,0.0252,0.0022</t>
-  </si>
-  <si>
-    <t>0.9612,0.0014,0.0314,0.0008</t>
-  </si>
-  <si>
-    <t>0.9891,0.0001,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.9935,0.0002,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9294,0.0041,0.0596,0.0021</t>
-  </si>
-  <si>
-    <t>0.9105,0.0067,0.0930,0.0037</t>
-  </si>
-  <si>
-    <t>0.7298,0.0034,0.3356,0.0021</t>
-  </si>
-  <si>
-    <t>0.5936,0.0017,0.5489,0.0011</t>
-  </si>
-  <si>
-    <t>0.1614,0.0016,0.9502,0.0001</t>
-  </si>
-  <si>
-    <t>0.6704,0.0199,0.4555,0.0010</t>
-  </si>
-  <si>
-    <t>0.9390,0.0046,0.0039,0.0424</t>
-  </si>
-  <si>
-    <t>0.8688,0.0128,0.0022,0.0508</t>
-  </si>
-  <si>
-    <t>0.8974,0.0172,0.0107,0.0355</t>
-  </si>
-  <si>
-    <t>0.8924,0.0173,0.0103,0.0255</t>
-  </si>
-  <si>
-    <t>0.8414,0.0098,0.0171,0.0651</t>
-  </si>
-  <si>
-    <t>0.9486,0.0037,0.0023,0.0226</t>
-  </si>
-  <si>
-    <t>0.9561,0.0009,0.0009,0.0451</t>
-  </si>
-  <si>
-    <t>0.9028,0.0105,0.0012,0.0173</t>
-  </si>
-  <si>
-    <t>0.0439,0.0440,0.9561,0.0067</t>
-  </si>
-  <si>
-    <t>0.7759,0.0447,0.1696,0.0217</t>
-  </si>
-  <si>
-    <t>0.9569,0.0029,0.0256,0.0027</t>
-  </si>
-  <si>
-    <t>0.6775,0.0179,0.4995,0.0013</t>
-  </si>
-  <si>
-    <t>0.0416,0.0097,0.9550,0.0015</t>
-  </si>
-  <si>
-    <t>0.7664,0.0072,0.2839,0.0029</t>
-  </si>
-  <si>
-    <t>0.0064,0.0135,0.9943,0.0001</t>
-  </si>
-  <si>
-    <t>0.6872,0.0021,0.4895,0.0006</t>
-  </si>
-  <si>
-    <t>0.0286,0.0747,0.9838,0.0008</t>
-  </si>
-  <si>
-    <t>0.5277,0.0079,0.5998,0.0020</t>
-  </si>
-  <si>
-    <t>0.2776,0.0083,0.8261,0.0009</t>
-  </si>
-  <si>
-    <t>0.9872,0.0001,0.0117,0.0001</t>
-  </si>
-  <si>
-    <t>0.9360,0.0018,0.0678,0.0012</t>
-  </si>
-  <si>
-    <t>0.9497,0.0015,0.0448,0.0014</t>
-  </si>
-  <si>
-    <t>0.8906,0.0179,0.0223,0.0268</t>
-  </si>
-  <si>
-    <t>0.9134,0.0190,0.0033,0.0120</t>
-  </si>
-  <si>
-    <t>0.9466,0.0041,0.0029,0.0288</t>
-  </si>
-  <si>
-    <t>0.9620,0.0030,0.0015,0.0156</t>
-  </si>
-  <si>
-    <t>0.9741,0.0042,0.0020,0.0044</t>
-  </si>
-  <si>
-    <t>0.8446,0.0017,0.0020,0.2088</t>
-  </si>
-  <si>
-    <t>0.9542,0.0026,0.0025,0.0236</t>
-  </si>
-  <si>
-    <t>0.9849,0.0008,0.0006,0.0058</t>
-  </si>
-  <si>
-    <t>0.1182,0.0180,0.9267,0.0014</t>
-  </si>
-  <si>
-    <t>0.1706,0.0207,0.8862,0.0034</t>
-  </si>
-  <si>
-    <t>0.0788,0.0078,0.9641,0.0004</t>
-  </si>
-  <si>
-    <t>0.6738,0.0145,0.4777,0.0008</t>
-  </si>
-  <si>
-    <t>0.7851,0.0066,0.3401,0.0010</t>
-  </si>
-  <si>
-    <t>0.9026,0.0017,0.0797,0.0045</t>
-  </si>
-  <si>
-    <t>0.9934,0.0001,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.6539,0.0141,0.4088,0.0041</t>
-  </si>
-  <si>
-    <t>0.9028,0.0046,0.0325,0.0169</t>
-  </si>
-  <si>
-    <t>0.9261,0.0006,0.0129,0.0137</t>
-  </si>
-  <si>
-    <t>0.9377,0.0005,0.0112,0.0110</t>
-  </si>
-  <si>
-    <t>0.8463,0.0004,0.0053,0.1151</t>
-  </si>
-  <si>
-    <t>0.9143,0.0000,0.0003,0.1273</t>
-  </si>
-  <si>
-    <t>0.9624,0.0023,0.0113,0.0020</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9385,0.0038,0.0042,0.0477</t>
+  </si>
+  <si>
+    <t>0.0644,0.0017,0.0003,0.9812</t>
+  </si>
+  <si>
+    <t>0.9295,0.0100,0.0028,0.0610</t>
+  </si>
+  <si>
+    <t>0.0948,0.0038,0.0021,0.9659</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9913,0.0118,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9931,0.0051,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0038,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9914,0.0140,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9233,0.0137,0.0771,0.0012</t>
+  </si>
+  <si>
+    <t>0.1905,0.0177,0.8483,0.0075</t>
+  </si>
+  <si>
+    <t>0.3370,0.0199,0.7997,0.0004</t>
+  </si>
+  <si>
+    <t>0.0293,0.0032,0.9770,0.0006</t>
+  </si>
+  <si>
+    <t>0.8225,0.0095,0.2090,0.0036</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9979,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.0547,0.9590,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.9898,0.0061,0.0017</t>
+  </si>
+  <si>
+    <t>0.0006,0.9987,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9827,0.0008,0.0213,0.0003</t>
+  </si>
+  <si>
+    <t>0.5755,0.0389,0.3494,0.0363</t>
+  </si>
+  <si>
+    <t>0.0016,0.0004,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.1587,0.0037,0.8796,0.0019</t>
+  </si>
+  <si>
+    <t>0.0063,0.0009,0.9921,0.0018</t>
+  </si>
+  <si>
+    <t>0.0011,0.0010,0.9958,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.0007,0.9973,0.0011</t>
+  </si>
+  <si>
+    <t>0.6988,0.2285,0.0685,0.0045</t>
+  </si>
+  <si>
+    <t>0.1024,0.8301,0.1264,0.0026</t>
+  </si>
+  <si>
+    <t>0.0033,0.0139,0.9937,0.0034</t>
+  </si>
+  <si>
+    <t>0.0279,0.8096,0.0645,0.0005</t>
+  </si>
+  <si>
+    <t>0.4917,0.4580,0.1244,0.0107</t>
+  </si>
+  <si>
+    <t>0.4105,0.0466,0.5317,0.0397</t>
+  </si>
+  <si>
+    <t>0.7417,0.4458,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.0079,0.9837,0.0831,0.0018</t>
+  </si>
+  <si>
+    <t>0.0096,0.9440,0.0322,0.0088</t>
+  </si>
+  <si>
+    <t>0.0592,0.0049,0.9169,0.0082</t>
+  </si>
+  <si>
+    <t>0.1906,0.0127,0.8000,0.0072</t>
+  </si>
+  <si>
+    <t>0.0059,0.0026,0.9900,0.0011</t>
+  </si>
+  <si>
+    <t>0.0121,0.2902,0.9514,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.9836,0.0365,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.0028,0.9950,0.0004</t>
+  </si>
+  <si>
+    <t>0.0183,0.6496,0.0122,0.7831</t>
+  </si>
+  <si>
+    <t>0.0044,0.9816,0.0320,0.0119</t>
+  </si>
+  <si>
+    <t>0.0051,0.9899,0.0163,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.9978,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.0314,0.9720,0.0027</t>
+  </si>
+  <si>
+    <t>0.0078,0.0312,0.9786,0.0007</t>
+  </si>
+  <si>
+    <t>0.0439,0.0077,0.9445,0.0054</t>
+  </si>
+  <si>
+    <t>0.1047,0.0007,0.9290,0.0026</t>
+  </si>
+  <si>
+    <t>0.0028,0.0052,0.9913,0.0010</t>
+  </si>
+  <si>
+    <t>0.0039,0.1659,0.9487,0.0013</t>
+  </si>
+  <si>
+    <t>0.9665,0.0498,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.9736,0.0171,0.0094,0.0021</t>
+  </si>
+  <si>
+    <t>0.9911,0.0024,0.0028,0.0021</t>
+  </si>
+  <si>
+    <t>0.0034,0.0270,0.9934,0.0090</t>
+  </si>
+  <si>
+    <t>0.9846,0.0053,0.0057,0.0026</t>
+  </si>
+  <si>
+    <t>0.9941,0.0045,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9935,0.0047,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.9724,0.8836,0.0006</t>
+  </si>
+  <si>
+    <t>0.0046,0.0042,0.9900,0.0017</t>
+  </si>
+  <si>
+    <t>0.0014,0.0080,0.9958,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9787,0.9779,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0057,0.9934,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.9970,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.9938,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9748,0.0049,0.0209,0.0007</t>
+  </si>
+  <si>
+    <t>0.6936,0.0741,0.2321,0.0022</t>
+  </si>
+  <si>
+    <t>0.0010,0.0095,0.9976,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,0.9931,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0055,0.9179,0.8602,0.0018</t>
+  </si>
+  <si>
+    <t>0.0006,0.9971,0.0220,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9796,0.8468,0.0007</t>
+  </si>
+  <si>
+    <t>0.0085,0.0012,0.0209,0.9873</t>
+  </si>
+  <si>
+    <t>0.0006,0.0016,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0174,0.0011,0.0003,0.9938</t>
+  </si>
+  <si>
+    <t>0.0059,0.0016,0.0007,0.9962</t>
+  </si>
+  <si>
+    <t>0.0335,0.0011,0.0028,0.9882</t>
+  </si>
+  <si>
+    <t>0.0045,0.0149,0.0015,0.9954</t>
+  </si>
+  <si>
+    <t>0.0004,0.9774,0.9863,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.7696,0.9788,0.0005</t>
+  </si>
+  <si>
+    <t>0.0527,0.6607,0.4004,0.0070</t>
+  </si>
+  <si>
+    <t>0.0023,0.7475,0.9336,0.0010</t>
+  </si>
+  <si>
+    <t>0.0281,0.8944,0.1726,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.9580,0.8330,0.0011</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9833,0.0188,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0029,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9976,0.0008,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0063,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0013,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9966,0.0013,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0033,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.1714,0.0032,0.9091,0.0024</t>
+  </si>
+  <si>
+    <t>0.8877,0.0085,0.1484,0.0016</t>
+  </si>
+  <si>
+    <t>0.8800,0.0028,0.0749,0.0119</t>
+  </si>
+  <si>
+    <t>0.0077,0.0001,0.9938,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.9939,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9969,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0081,0.9897,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0265,0.9683,0.0045,0.0019</t>
+  </si>
+  <si>
+    <t>0.0011,0.9978,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.9964,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.5947,0.4570,0.0132,0.0022</t>
+  </si>
+  <si>
+    <t>0.8623,0.0277,0.1327,0.0094</t>
+  </si>
+  <si>
+    <t>0.0136,0.0069,0.9802,0.0068</t>
+  </si>
+  <si>
+    <t>0.4017,0.0174,0.6745,0.0137</t>
+  </si>
+  <si>
+    <t>0.8715,0.0354,0.1112,0.0114</t>
+  </si>
+  <si>
+    <t>0.0523,0.0467,0.0680,0.9097</t>
+  </si>
+  <si>
+    <t>0.0013,0.9960,0.0074,0.0011</t>
+  </si>
+  <si>
+    <t>0.0029,0.9915,0.0016,0.0040</t>
+  </si>
+  <si>
+    <t>0.0014,0.9904,0.0045,0.0051</t>
+  </si>
+  <si>
+    <t>0.0008,0.9946,0.2027,0.0018</t>
+  </si>
+  <si>
+    <t>0.0034,0.9945,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.3886,0.7307,0.0076,0.0027</t>
+  </si>
+  <si>
+    <t>0.4587,0.7145,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.9929,0.0061,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9942,0.0006,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9907,0.0030,0.0027,0.0019</t>
+  </si>
+  <si>
+    <t>0.9926,0.0026,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9731,0.0442,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9847,0.0087,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.9961,0.0007,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.8978,0.9979,0.0005</t>
+  </si>
+  <si>
+    <t>0.0051,0.9050,0.8343,0.0017</t>
+  </si>
+  <si>
+    <t>0.0038,0.0387,0.9866,0.0018</t>
+  </si>
+  <si>
+    <t>0.1113,0.0084,0.9058,0.0011</t>
+  </si>
+  <si>
+    <t>0.9821,0.0022,0.0052,0.0025</t>
+  </si>
+  <si>
+    <t>0.5402,0.0017,0.5797,0.0063</t>
+  </si>
+  <si>
+    <t>0.0699,0.0017,0.9711,0.0009</t>
+  </si>
+  <si>
+    <t>0.6855,0.0087,0.5128,0.0017</t>
+  </si>
+  <si>
+    <t>0.1974,0.0024,0.0017,0.9288</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0017,0.0110,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0080,0.0002,0.0046,0.9951</t>
+  </si>
+  <si>
+    <t>0.0011,0.9796,0.2648,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0395,0.9478,0.0044,0.0104</t>
+  </si>
+  <si>
+    <t>0.9892,0.0039,0.0014,0.0028</t>
+  </si>
+  <si>
+    <t>0.9079,0.1164,0.0039,0.0020</t>
+  </si>
+  <si>
+    <t>0.9776,0.0053,0.0134,0.0016</t>
+  </si>
+  <si>
+    <t>0.2604,0.0091,0.0459,0.7900</t>
+  </si>
+  <si>
+    <t>0.9936,0.0008,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.0286,0.0731,0.9447,0.0346</t>
+  </si>
+  <si>
+    <t>0.9626,0.0059,0.0019,0.0262</t>
+  </si>
+  <si>
+    <t>0.9791,0.0094,0.0018,0.0056</t>
+  </si>
+  <si>
+    <t>0.0954,0.8733,0.0295,0.0122</t>
+  </si>
+  <si>
+    <t>0.9772,0.0080,0.0044,0.0034</t>
+  </si>
+  <si>
+    <t>0.9659,0.0298,0.0055,0.0020</t>
+  </si>
+  <si>
+    <t>0.0756,0.8308,0.1433,0.0074</t>
+  </si>
+  <si>
+    <t>0.8770,0.0370,0.0791,0.0085</t>
+  </si>
+  <si>
+    <t>0.8704,0.0406,0.1142,0.0037</t>
+  </si>
+  <si>
+    <t>0.9916,0.0024,0.0022,0.0011</t>
+  </si>
+  <si>
+    <t>0.9949,0.0025,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9910,0.0005,0.0033,0.0022</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9704,0.0127,0.0169,0.0021</t>
+  </si>
+  <si>
+    <t>0.9940,0.0016,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9707,0.0230,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.4725,0.6876,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.7974,0.2644,0.0061,0.0037</t>
+  </si>
+  <si>
+    <t>0.4813,0.1494,0.5335,0.0280</t>
+  </si>
+  <si>
+    <t>0.9944,0.0052,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9776,0.0231,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.9871,0.0041,0.0053,0.0012</t>
+  </si>
+  <si>
+    <t>0.9794,0.0196,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.0029,0.0137,0.9973,0.0007</t>
+  </si>
+  <si>
+    <t>0.9800,0.0124,0.0045,0.0023</t>
+  </si>
+  <si>
+    <t>0.0009,0.0056,0.9958,0.0003</t>
+  </si>
+  <si>
+    <t>0.0039,0.0733,0.9884,0.0042</t>
+  </si>
+  <si>
+    <t>0.0060,0.0013,0.9936,0.0013</t>
+  </si>
+  <si>
+    <t>0.0264,0.0293,0.9519,0.0045</t>
+  </si>
+  <si>
+    <t>0.0004,0.0060,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0004,0.9972,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9969,0.0008</t>
+  </si>
+  <si>
+    <t>0.1652,0.0238,0.8355,0.0217</t>
+  </si>
+  <si>
+    <t>0.3955,0.0043,0.7952,0.0017</t>
+  </si>
+  <si>
+    <t>0.8376,0.0821,0.0865,0.0058</t>
+  </si>
+  <si>
+    <t>0.3544,0.0152,0.7881,0.0012</t>
+  </si>
+  <si>
+    <t>0.1864,0.3346,0.5466,0.0042</t>
+  </si>
+  <si>
+    <t>0.2096,0.0958,0.6867,0.0022</t>
+  </si>
+  <si>
+    <t>0.6842,0.0051,0.4472,0.0048</t>
+  </si>
+  <si>
+    <t>0.3442,0.4272,0.2491,0.0155</t>
+  </si>
+  <si>
+    <t>0.1756,0.8852,0.0073,0.0007</t>
+  </si>
+  <si>
+    <t>0.8124,0.3445,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9573,0.0572,0.0013,0.0020</t>
+  </si>
+  <si>
+    <t>0.9921,0.0129,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7921,0.4443,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.8988,0.0281,0.0750,0.0045</t>
+  </si>
+  <si>
+    <t>0.9487,0.0018,0.0761,0.0011</t>
+  </si>
+  <si>
+    <t>0.8986,0.0124,0.0605,0.0106</t>
+  </si>
+  <si>
+    <t>0.8151,0.0129,0.3089,0.0026</t>
+  </si>
+  <si>
+    <t>0.1418,0.0013,0.9008,0.0081</t>
+  </si>
+  <si>
+    <t>0.0075,0.0080,0.9761,0.0266</t>
+  </si>
+  <si>
+    <t>0.0093,0.6874,0.8087,0.0099</t>
+  </si>
+  <si>
+    <t>0.0152,0.0580,0.9773,0.0014</t>
+  </si>
+  <si>
+    <t>0.0989,0.0211,0.9003,0.0034</t>
+  </si>
+  <si>
+    <t>0.0041,0.0846,0.9372,0.0030</t>
+  </si>
+  <si>
+    <t>0.9957,0.0015,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9947,0.0027,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9951,0.0041,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9824,0.0062,0.0033,0.0031</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0066,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0030,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.0159,0.0201,0.9874,0.0033</t>
+  </si>
+  <si>
+    <t>0.0234,0.0221,0.9506,0.0067</t>
+  </si>
+  <si>
+    <t>0.8227,0.0118,0.1884,0.0070</t>
+  </si>
+  <si>
+    <t>0.0123,0.0270,0.9725,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.0010,0.9878,0.0025</t>
+  </si>
+  <si>
+    <t>0.0042,0.0048,0.9883,0.0014</t>
+  </si>
+  <si>
+    <t>0.0020,0.0024,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0244,0.0018,0.9751,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.0068,0.9931,0.0019</t>
+  </si>
+  <si>
+    <t>0.0034,0.0031,0.9935,0.0009</t>
+  </si>
+  <si>
+    <t>0.0371,0.0144,0.9394,0.0084</t>
+  </si>
+  <si>
+    <t>0.8734,0.0069,0.1810,0.0043</t>
+  </si>
+  <si>
+    <t>0.2656,0.0007,0.8614,0.0012</t>
+  </si>
+  <si>
+    <t>0.9777,0.0001,0.0139,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0060,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9924,0.0064,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0025,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9886,0.0111,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9973,0.0009,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0119,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9915,0.0058,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9962,0.0015,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.0108,0.0044,0.9849,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0119,0.9955,0.0011</t>
+  </si>
+  <si>
+    <t>0.0087,0.0042,0.9897,0.0005</t>
+  </si>
+  <si>
+    <t>0.0112,0.1237,0.9139,0.0023</t>
+  </si>
+  <si>
+    <t>0.0081,0.0106,0.9877,0.0005</t>
+  </si>
+  <si>
+    <t>0.0932,0.0060,0.8423,0.0598</t>
+  </si>
+  <si>
+    <t>0.3056,0.0042,0.8048,0.0011</t>
+  </si>
+  <si>
+    <t>0.0457,0.0073,0.7556,0.1014</t>
+  </si>
+  <si>
+    <t>0.5624,0.0006,0.0033,0.5486</t>
+  </si>
+  <si>
+    <t>0.0157,0.0166,0.0035,0.9867</t>
+  </si>
+  <si>
+    <t>0.0243,0.0022,0.0010,0.9899</t>
+  </si>
+  <si>
+    <t>0.0026,0.0005,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0018,0.0047,0.0001,0.9982</t>
+  </si>
+  <si>
+    <t>0.9157,0.0048,0.0033,0.0562</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,10 +2194,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,10 +2208,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2236,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,10 +2250,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2600,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>259</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3622,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3930,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
